--- a/data/trans_orig/P1401-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1401-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de cáncer en 2012</t>
+          <t>Población con diagnóstico de cáncer en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5360</t>
+          <t>4358</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1880</t>
+          <t>1884</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10833</t>
+          <t>10662</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2823</t>
+          <t>2794</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13936</t>
+          <t>12840</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>431851</t>
+          <t>432853</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>303621</t>
+          <t>303792</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>312574</t>
+          <t>312570</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>737729</t>
+          <t>738825</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>748842</t>
+          <t>748871</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1052</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9351</t>
+          <t>10317</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1978</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13186</t>
+          <t>12796</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5126</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18921</t>
+          <t>19170</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>409446</t>
+          <t>408480</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>417745</t>
+          <t>417738</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>324825</t>
+          <t>325215</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>336033</t>
+          <t>335893</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>737887</t>
+          <t>737638</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>751718</t>
+          <t>751682</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8247</t>
+          <t>8033</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25765</t>
+          <t>23825</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3918</t>
+          <t>3970</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15907</t>
+          <t>15797</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14229</t>
+          <t>15406</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32979</t>
+          <t>34961</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>603650</t>
+          <t>605590</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>621168</t>
+          <t>621382</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>244222</t>
+          <t>244332</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>256211</t>
+          <t>256159</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>856565</t>
+          <t>854583</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>875315</t>
+          <t>874138</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8492</t>
+          <t>8395</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25937</t>
+          <t>25881</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7726</t>
+          <t>6874</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27025</t>
+          <t>26212</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,47 +1811,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>3,43%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>29497</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>19482</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>44025</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>1,01%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>29497</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>18955</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>44469</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1133072</t>
+          <t>1133128</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1150517</t>
+          <t>1150614</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>737697</t>
+          <t>738510</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>756996</t>
+          <t>757848</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,47 +1924,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
+          <t>99,1%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1769</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1894234</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1879706</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1904249</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>98,47%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>97,71%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>98,99%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1769</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1894234</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1879262</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1904776</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>98,47%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>97,69%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>99,01%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>946</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9681</t>
+          <t>9731</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10834</t>
+          <t>11697</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28012</t>
+          <t>29180</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14900</t>
+          <t>14042</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34621</t>
+          <t>33777</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>500915</t>
+          <t>500865</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>509608</t>
+          <t>509650</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>732234</t>
+          <t>731066</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>749412</t>
+          <t>748549</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1236222</t>
+          <t>1237066</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1255943</t>
+          <t>1256801</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4491</t>
+          <t>4563</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11218</t>
+          <t>11118</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29923</t>
+          <t>29890</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12168</t>
+          <t>12722</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30372</t>
+          <t>31546</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>262391</t>
+          <t>262319</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1079428</t>
+          <t>1079461</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1098133</t>
+          <t>1098233</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1345861</t>
+          <t>1344687</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1364065</t>
+          <t>1363511</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27394</t>
+          <t>28280</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53043</t>
+          <t>55190</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>54706</t>
+          <t>54783</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>91175</t>
+          <t>91632</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>91407</t>
+          <t>91400</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>135299</t>
+          <t>133950</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3368867</t>
+          <t>3366720</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3394516</t>
+          <t>3393630</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3455740</t>
+          <t>3455283</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3492209</t>
+          <t>3492132</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6833526</t>
+          <t>6834875</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6877418</t>
+          <t>6877425</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de cáncer en 2016</t>
+          <t>Población con diagnóstico de cáncer en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>968</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11168</t>
+          <t>10169</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3385</t>
+          <t>4199</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15544</t>
+          <t>16071</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6948</t>
+          <t>7050</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20894</t>
+          <t>22135</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>417924</t>
+          <t>418923</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>428115</t>
+          <t>428124</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>331511</t>
+          <t>330984</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>343670</t>
+          <t>342856</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>755253</t>
+          <t>754012</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>769199</t>
+          <t>769097</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>735</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7219</t>
+          <t>7944</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12803</t>
+          <t>10679</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2135</t>
+          <t>1962</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14470</t>
+          <t>14383</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>370008</t>
+          <t>369283</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>376493</t>
+          <t>376492</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>359470</t>
+          <t>361594</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>735030</t>
+          <t>735117</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>747365</t>
+          <t>747538</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2460</t>
+          <t>2596</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12922</t>
+          <t>13693</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3333</t>
+          <t>3142</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15434</t>
+          <t>15017</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7072</t>
+          <t>7975</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23349</t>
+          <t>23103</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>508992</t>
+          <t>508221</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>519454</t>
+          <t>519318</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>150689</t>
+          <t>151106</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>162790</t>
+          <t>162981</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>664687</t>
+          <t>664933</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>680964</t>
+          <t>680061</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3637</t>
+          <t>3636</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14003</t>
+          <t>14599</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10474</t>
+          <t>10915</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28485</t>
+          <t>29215</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16802</t>
+          <t>16465</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37406</t>
+          <t>37953</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1135635</t>
+          <t>1135039</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1146001</t>
+          <t>1146002</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>797391</t>
+          <t>796661</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>815402</t>
+          <t>814961</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1938108</t>
+          <t>1937561</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1958712</t>
+          <t>1959049</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4562</t>
+          <t>4860</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16273</t>
+          <t>16672</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11810</t>
+          <t>11907</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31084</t>
+          <t>30619</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19356</t>
+          <t>19578</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42615</t>
+          <t>40652</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>604433</t>
+          <t>604034</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>616144</t>
+          <t>615846</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>707160</t>
+          <t>707625</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>726434</t>
+          <t>726337</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1316335</t>
+          <t>1318298</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1339594</t>
+          <t>1339372</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,56%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6479</t>
+          <t>7517</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22234</t>
+          <t>21483</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6996</t>
+          <t>7358</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22193</t>
+          <t>23155</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>285126</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>287145</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1059791</t>
+          <t>1060542</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1075546</t>
+          <t>1074508</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1346977</t>
+          <t>1346015</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1362174</t>
+          <t>1361812</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20651</t>
+          <t>20183</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41586</t>
+          <t>40587</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>55604</t>
+          <t>54828</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>90516</t>
+          <t>90602</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>82453</t>
+          <t>82930</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>125495</t>
+          <t>123885</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3344136</t>
+          <t>3345135</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3365071</t>
+          <t>3365539</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3441080</t>
+          <t>3440994</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3475992</t>
+          <t>3476768</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6791823</t>
+          <t>6793433</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6834865</t>
+          <t>6834388</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5807,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de cáncer en 2023</t>
+          <t>Población con diagnóstico de cáncer en 2023 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6002,12 +6002,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9817</t>
+          <t>9806</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24861</t>
+          <t>24933</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4744</t>
+          <t>4567</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13761</t>
+          <t>13384</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17073</t>
+          <t>17018</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33040</t>
+          <t>33283</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6092,7 +6092,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -6115,12 +6115,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>480351</t>
+          <t>480279</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>495395</t>
+          <t>495406</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>433706</t>
+          <t>434083</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>442723</t>
+          <t>442900</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>919639</t>
+          <t>919396</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>935606</t>
+          <t>935661</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5266</t>
+          <t>5473</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16472</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>3844</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11555</t>
+          <t>12045</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10716</t>
+          <t>10872</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23866</t>
+          <t>24126</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -6458,12 +6458,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>434881</t>
+          <t>434470</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>446087</t>
+          <t>445880</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>369728</t>
+          <t>369238</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>377673</t>
+          <t>377439</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>808770</t>
+          <t>808510</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>821920</t>
+          <t>821764</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -6688,12 +6688,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3530</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22898</t>
+          <t>22640</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5693</t>
+          <t>5794</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5032</t>
+          <t>5618</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24616</t>
+          <t>24877</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -6801,12 +6801,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>643571</t>
+          <t>643829</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>662939</t>
+          <t>663425</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6836,12 +6836,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>161218</t>
+          <t>161117</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165937</t>
+          <t>165773</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>808764</t>
+          <t>808503</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>828348</t>
+          <t>827762</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -7031,12 +7031,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14129</t>
+          <t>13612</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29835</t>
+          <t>30450</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7466</t>
+          <t>7385</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21841</t>
+          <t>22689</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22950</t>
+          <t>23273</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46159</t>
+          <t>45594</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -7144,12 +7144,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1003336</t>
+          <t>1002721</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1019042</t>
+          <t>1019559</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>955590</t>
+          <t>954742</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>969965</t>
+          <t>970046</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1964442</t>
+          <t>1965007</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1987651</t>
+          <t>1987328</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -7374,12 +7374,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3849</t>
+          <t>3751</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13091</t>
+          <t>12986</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16741</t>
+          <t>17152</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34031</t>
+          <t>33449</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23494</t>
+          <t>23132</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43593</t>
+          <t>41347</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -7487,12 +7487,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>460958</t>
+          <t>461063</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>470200</t>
+          <t>470298</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>804334</t>
+          <t>804916</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>821624</t>
+          <t>821213</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1268821</t>
+          <t>1271067</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1288920</t>
+          <t>1289282</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,24%</t>
         </is>
       </c>
     </row>
@@ -7717,12 +7717,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4080</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13202</t>
+          <t>13091</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25414</t>
+          <t>25816</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13117</t>
+          <t>13065</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>25559</t>
+          <t>24901</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -7830,12 +7830,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>236427</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>735278</t>
+          <t>734876</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>747490</t>
+          <t>747601</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>975641</t>
+          <t>976299</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>988083</t>
+          <t>988135</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>48027</t>
+          <t>47014</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>81994</t>
+          <t>81276</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>60502</t>
+          <t>60200</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>91365</t>
+          <t>90100</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>117183</t>
+          <t>118275</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>164541</t>
+          <t>165491</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3288768</t>
+          <t>3289486</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3322735</t>
+          <t>3323748</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3480783</t>
+          <t>3482048</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3511646</t>
+          <t>3511948</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6778369</t>
+          <t>6777419</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6825727</t>
+          <t>6824635</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,3%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1401-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1401-Clase-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4358</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1884</t>
+          <t>1889</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10662</t>
+          <t>10516</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2794</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12840</t>
+          <t>13570</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>432853</t>
+          <t>431910</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>303792</t>
+          <t>303938</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>312570</t>
+          <t>312565</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>738825</t>
+          <t>738095</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>748871</t>
+          <t>749637</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>1079</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>10064</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12796</t>
+          <t>14160</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,47 +1125,47 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>4,19%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>10039</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>4762</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>18934</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>0,63%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>3,79%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>10039</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>5126</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>19170</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>408480</t>
+          <t>408733</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>417738</t>
+          <t>417718</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>325215</t>
+          <t>323851</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>335893</t>
+          <t>336022</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,47 +1238,47 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
+          <t>99,41%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>671</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>746769</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>737874</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>752046</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>98,67%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>97,5%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>99,37%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>671</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>746769</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>737638</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>751682</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>98,67%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>97,47%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8033</t>
+          <t>8072</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23825</t>
+          <t>24174</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3970</t>
+          <t>4034</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15797</t>
+          <t>16481</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15406</t>
+          <t>13188</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34961</t>
+          <t>33041</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>605590</t>
+          <t>605241</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>621382</t>
+          <t>621343</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>244332</t>
+          <t>243648</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>256159</t>
+          <t>256095</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>854583</t>
+          <t>856503</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>874138</t>
+          <t>876356</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,52%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8395</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25881</t>
+          <t>25232</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6874</t>
+          <t>7370</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26212</t>
+          <t>26930</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19482</t>
+          <t>19528</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44025</t>
+          <t>45383</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1133128</t>
+          <t>1133777</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1150614</t>
+          <t>1151008</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>738510</t>
+          <t>737792</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>757848</t>
+          <t>757352</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1879706</t>
+          <t>1878348</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1904249</t>
+          <t>1904203</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9731</t>
+          <t>8948</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11697</t>
+          <t>10846</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29180</t>
+          <t>28432</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14042</t>
+          <t>14485</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33777</t>
+          <t>34070</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>500865</t>
+          <t>501648</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>731066</t>
+          <t>731814</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>748549</t>
+          <t>749400</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1237066</t>
+          <t>1236773</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1256801</t>
+          <t>1256358</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4563</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11118</t>
+          <t>11970</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29890</t>
+          <t>29503</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12722</t>
+          <t>12098</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31546</t>
+          <t>31602</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>262319</t>
+          <t>261530</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1079461</t>
+          <t>1079848</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1098233</t>
+          <t>1097381</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1344687</t>
+          <t>1344631</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1363511</t>
+          <t>1364135</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28280</t>
+          <t>27271</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>55190</t>
+          <t>53704</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>54783</t>
+          <t>56020</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>91632</t>
+          <t>89759</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>91400</t>
+          <t>90470</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>133950</t>
+          <t>137533</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3366720</t>
+          <t>3368206</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3393630</t>
+          <t>3394639</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3455283</t>
+          <t>3457156</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3492132</t>
+          <t>3490895</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6834875</t>
+          <t>6831292</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6877425</t>
+          <t>6878355</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10169</t>
+          <t>9875</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4199</t>
+          <t>4075</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16071</t>
+          <t>15290</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7050</t>
+          <t>6438</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22135</t>
+          <t>21983</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>418923</t>
+          <t>419217</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>428124</t>
+          <t>428027</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>330984</t>
+          <t>331765</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>342856</t>
+          <t>342980</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>754012</t>
+          <t>754164</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>769097</t>
+          <t>769709</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>729</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7944</t>
+          <t>7700</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10679</t>
+          <t>11545</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1962</t>
+          <t>1828</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14383</t>
+          <t>13829</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>369283</t>
+          <t>369527</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>376492</t>
+          <t>376498</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>361594</t>
+          <t>360728</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>735117</t>
+          <t>735671</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>747538</t>
+          <t>747672</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2596</t>
+          <t>2791</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13693</t>
+          <t>14053</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>3123</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15017</t>
+          <t>15541</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7975</t>
+          <t>7869</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23103</t>
+          <t>24557</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>508221</t>
+          <t>507861</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>519318</t>
+          <t>519123</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>151106</t>
+          <t>150582</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>162981</t>
+          <t>163000</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>664933</t>
+          <t>663479</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>680061</t>
+          <t>680167</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3636</t>
+          <t>3454</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14599</t>
+          <t>14468</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10915</t>
+          <t>10621</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29215</t>
+          <t>28841</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16465</t>
+          <t>16970</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37953</t>
+          <t>37917</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1135039</t>
+          <t>1135170</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1146002</t>
+          <t>1146184</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>796661</t>
+          <t>797035</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>814961</t>
+          <t>815255</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1937561</t>
+          <t>1937597</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1959049</t>
+          <t>1958544</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4860</t>
+          <t>4574</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16672</t>
+          <t>15795</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11907</t>
+          <t>12471</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30619</t>
+          <t>31657</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19578</t>
+          <t>19715</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40652</t>
+          <t>42544</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>604034</t>
+          <t>604911</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>615846</t>
+          <t>616132</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>707625</t>
+          <t>706587</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>726337</t>
+          <t>725773</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1318298</t>
+          <t>1316406</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1339372</t>
+          <t>1339235</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,55%</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7517</t>
+          <t>6768</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21483</t>
+          <t>21968</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7358</t>
+          <t>6707</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23155</t>
+          <t>22022</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1060542</t>
+          <t>1060057</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1074508</t>
+          <t>1075257</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1346015</t>
+          <t>1347148</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1361812</t>
+          <t>1362463</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20183</t>
+          <t>20328</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40587</t>
+          <t>41949</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>54828</t>
+          <t>54167</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>90602</t>
+          <t>89208</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>82930</t>
+          <t>81175</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>123885</t>
+          <t>124248</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3345135</t>
+          <t>3343773</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3365539</t>
+          <t>3365394</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3440994</t>
+          <t>3442388</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3476768</t>
+          <t>3477429</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6793433</t>
+          <t>6793070</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6834388</t>
+          <t>6836143</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -5997,32 +5997,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>15623</t>
+          <t>17588</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9806</t>
+          <t>11298</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24933</t>
+          <t>26400</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6032,32 +6032,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8312</t>
+          <t>9450</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4567</t>
+          <t>5554</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13384</t>
+          <t>15523</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6067,32 +6067,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>23935</t>
+          <t>27037</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17018</t>
+          <t>18976</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33283</t>
+          <t>37900</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -6110,32 +6110,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>489589</t>
+          <t>533030</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>480279</t>
+          <t>524218</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>495406</t>
+          <t>539320</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6145,32 +6145,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>439155</t>
+          <t>478961</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>434083</t>
+          <t>472888</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>442900</t>
+          <t>482857</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6180,32 +6180,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>928744</t>
+          <t>1011992</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>919396</t>
+          <t>1001129</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>935661</t>
+          <t>1020053</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,17%</t>
         </is>
       </c>
     </row>
@@ -6223,17 +6223,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6258,17 +6258,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6293,17 +6293,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6340,32 +6340,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9819</t>
+          <t>10958</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5473</t>
+          <t>5902</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>18486</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6375,32 +6375,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6835</t>
+          <t>7761</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3844</t>
+          <t>4432</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12045</t>
+          <t>12894</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6410,32 +6410,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>16654</t>
+          <t>18719</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10872</t>
+          <t>12344</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24126</t>
+          <t>28069</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -6453,32 +6453,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>441534</t>
+          <t>471309</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>434470</t>
+          <t>463781</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>445880</t>
+          <t>476365</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6488,32 +6488,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>374448</t>
+          <t>414042</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>369238</t>
+          <t>408909</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>377439</t>
+          <t>417371</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6523,32 +6523,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>815982</t>
+          <t>885351</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>808510</t>
+          <t>876001</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>821764</t>
+          <t>891726</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -6566,17 +6566,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>451353</t>
+          <t>482267</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>451353</t>
+          <t>482267</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>451353</t>
+          <t>482267</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6601,17 +6601,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>381283</t>
+          <t>421803</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>381283</t>
+          <t>421803</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>381283</t>
+          <t>421803</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6636,17 +6636,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>832636</t>
+          <t>904070</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>832636</t>
+          <t>904070</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>832636</t>
+          <t>904070</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6683,32 +6683,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>11851</t>
+          <t>12501</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>7243</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22640</t>
+          <t>20498</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6718,32 +6718,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2820</t>
+          <t>2973</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5794</t>
+          <t>6149</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6753,32 +6753,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>14671</t>
+          <t>15474</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5618</t>
+          <t>10072</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24877</t>
+          <t>23881</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -6796,32 +6796,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>654618</t>
+          <t>457144</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>643829</t>
+          <t>449147</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>663425</t>
+          <t>462402</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6831,32 +6831,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>164091</t>
+          <t>184524</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>161117</t>
+          <t>181348</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165773</t>
+          <t>186347</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6866,32 +6866,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>818709</t>
+          <t>641669</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>808503</t>
+          <t>633262</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>827762</t>
+          <t>647071</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -6909,17 +6909,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>666469</t>
+          <t>469645</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>666469</t>
+          <t>469645</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>666469</t>
+          <t>469645</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6944,17 +6944,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6979,17 +6979,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>833380</t>
+          <t>657143</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>833380</t>
+          <t>657143</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>833380</t>
+          <t>657143</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7026,32 +7026,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20377</t>
+          <t>21116</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13612</t>
+          <t>14095</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30450</t>
+          <t>31740</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7061,32 +7061,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14752</t>
+          <t>16218</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7385</t>
+          <t>11635</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22689</t>
+          <t>22737</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7096,32 +7096,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>35129</t>
+          <t>37334</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23273</t>
+          <t>28926</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45594</t>
+          <t>48600</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -7139,32 +7139,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1012794</t>
+          <t>1108000</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1002721</t>
+          <t>1097376</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1019559</t>
+          <t>1115021</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7174,32 +7174,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>962679</t>
+          <t>844285</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>954742</t>
+          <t>837766</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>970046</t>
+          <t>848868</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7209,32 +7209,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1975472</t>
+          <t>1952285</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1965007</t>
+          <t>1941019</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1987328</t>
+          <t>1960693</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,55%</t>
         </is>
       </c>
     </row>
@@ -7252,17 +7252,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1033171</t>
+          <t>1129116</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1033171</t>
+          <t>1129116</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1033171</t>
+          <t>1129116</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7287,17 +7287,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>977431</t>
+          <t>860503</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>977431</t>
+          <t>860503</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>977431</t>
+          <t>860503</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7322,17 +7322,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2010601</t>
+          <t>1989619</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2010601</t>
+          <t>1989619</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2010601</t>
+          <t>1989619</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7369,32 +7369,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>7227</t>
+          <t>7625</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3751</t>
+          <t>3918</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12986</t>
+          <t>14131</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7404,32 +7404,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>24876</t>
+          <t>26546</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17152</t>
+          <t>19636</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33449</t>
+          <t>36134</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7439,17 +7439,17 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>32103</t>
+          <t>34171</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23132</t>
+          <t>25345</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41347</t>
+          <t>43668</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -7482,32 +7482,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>466822</t>
+          <t>559351</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>461063</t>
+          <t>552845</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>470298</t>
+          <t>563058</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7517,32 +7517,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>813489</t>
+          <t>802874</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>804916</t>
+          <t>793286</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>821213</t>
+          <t>809784</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7552,17 +7552,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1280311</t>
+          <t>1362225</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1271067</t>
+          <t>1352728</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1289282</t>
+          <t>1371051</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,18%</t>
         </is>
       </c>
     </row>
@@ -7595,17 +7595,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7630,17 +7630,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>838365</t>
+          <t>829420</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>838365</t>
+          <t>829420</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>838365</t>
+          <t>829420</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7665,17 +7665,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1312414</t>
+          <t>1396396</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1312414</t>
+          <t>1396396</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1312414</t>
+          <t>1396396</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7697,7 +7697,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7747,32 +7747,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>18455</t>
+          <t>19836</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13091</t>
+          <t>14121</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25816</t>
+          <t>27477</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7782,17 +7782,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>18455</t>
+          <t>19836</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13065</t>
+          <t>13771</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24901</t>
+          <t>27415</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -7825,7 +7825,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -7860,32 +7860,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>742237</t>
+          <t>823760</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>734876</t>
+          <t>816119</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>747601</t>
+          <t>829475</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7895,17 +7895,17 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>982745</t>
+          <t>1060988</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>976299</t>
+          <t>1053409</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>988135</t>
+          <t>1067053</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -7938,17 +7938,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7973,17 +7973,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760692</t>
+          <t>843596</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760692</t>
+          <t>843596</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760692</t>
+          <t>843596</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8008,17 +8008,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001200</t>
+          <t>1080824</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001200</t>
+          <t>1080824</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001200</t>
+          <t>1080824</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8055,32 +8055,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>64898</t>
+          <t>69788</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>47014</t>
+          <t>55776</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>81276</t>
+          <t>87710</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8090,32 +8090,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>76049</t>
+          <t>82783</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>60200</t>
+          <t>69768</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>90100</t>
+          <t>96504</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8125,32 +8125,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>140947</t>
+          <t>152571</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>118275</t>
+          <t>134038</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>165491</t>
+          <t>174368</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -8168,32 +8168,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3305864</t>
+          <t>3366062</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3289486</t>
+          <t>3348140</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3323748</t>
+          <t>3380074</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8203,32 +8203,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3496099</t>
+          <t>3548447</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3482048</t>
+          <t>3534726</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3511948</t>
+          <t>3561462</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8238,32 +8238,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6801963</t>
+          <t>6914509</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6777419</t>
+          <t>6892712</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6824635</t>
+          <t>6933042</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -8281,17 +8281,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3370762</t>
+          <t>3435850</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3370762</t>
+          <t>3435850</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3370762</t>
+          <t>3435850</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8316,17 +8316,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3572148</t>
+          <t>3631230</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3572148</t>
+          <t>3631230</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3572148</t>
+          <t>3631230</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8351,17 +8351,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6942910</t>
+          <t>7067080</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6942910</t>
+          <t>7067080</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6942910</t>
+          <t>7067080</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
